--- a/verification/cases/roundtrip/formulas_information/init.xlsx
+++ b/verification/cases/roundtrip/formulas_information/init.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2BE645-0818-644B-AB3B-95A37EF07B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3EF86D0-D603-4986-872F-ECC9E47F124A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6660" yWindow="1940" windowWidth="32180" windowHeight="23180" xr2:uid="{CE99472F-67E3-574B-A632-EE6DAD76FAED}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{CE99472F-67E3-574B-A632-EE6DAD76FAED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -688,7 +688,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -711,24 +711,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17806C9A-6330-1B4C-B463-2FF919A4655E}">
   <dimension ref="B2:O160"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.296875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.69921875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:14" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
@@ -745,7 +745,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -760,7 +760,7 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
@@ -777,7 +777,7 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
@@ -794,7 +794,7 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>1</v>
       </c>
@@ -813,7 +813,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>2</v>
       </c>
@@ -832,7 +832,7 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
@@ -851,7 +851,7 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
@@ -870,7 +870,7 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
@@ -889,7 +889,7 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
@@ -908,7 +908,7 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
@@ -928,7 +928,7 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="b">
         <v>1</v>
       </c>
@@ -947,7 +947,7 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="b">
         <v>0</v>
       </c>
@@ -966,7 +966,7 @@
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>10</v>
       </c>
@@ -986,7 +986,7 @@
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>11</v>
       </c>
@@ -1006,7 +1006,7 @@
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>12</v>
       </c>
@@ -1026,7 +1026,7 @@
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>13</v>
       </c>
@@ -1046,7 +1046,7 @@
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>14</v>
       </c>
@@ -1066,7 +1066,7 @@
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
         <v>15</v>
       </c>
@@ -1086,7 +1086,7 @@
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1106,7 +1106,7 @@
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B22" s="3" t="s">
         <v>17</v>
       </c>
@@ -1126,7 +1126,7 @@
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B23" s="3" t="s">
         <v>18</v>
       </c>
@@ -1145,7 +1145,7 @@
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>19</v>
       </c>
@@ -1164,7 +1164,7 @@
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
         <v>20</v>
       </c>
@@ -1183,7 +1183,7 @@
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>20</v>
       </c>
@@ -1200,7 +1200,7 @@
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -1215,7 +1215,7 @@
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>22</v>
       </c>
@@ -1232,7 +1232,7 @@
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B29" s="9" t="s">
         <v>23</v>
       </c>
@@ -1265,9 +1265,9 @@
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B30" s="5" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B30:B50" si="0">B5</f>
         <v>Blank Cell</v>
       </c>
       <c r="C30" s="10" t="b">
@@ -1307,9 +1307,9 @@
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B31" s="5" t="str">
-        <f>B6</f>
+        <f t="shared" si="0"/>
         <v>Zero</v>
       </c>
       <c r="C31" s="10" t="b">
@@ -1349,9 +1349,9 @@
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B32" s="5" t="str">
-        <f>B7</f>
+        <f t="shared" si="0"/>
         <v>One</v>
       </c>
       <c r="C32" s="10" t="b">
@@ -1391,9 +1391,9 @@
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B33" s="5" t="str">
-        <f>B8</f>
+        <f t="shared" si="0"/>
         <v>Negative One</v>
       </c>
       <c r="C33" s="10" t="b">
@@ -1433,9 +1433,9 @@
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B34" s="5" t="str">
-        <f>B9</f>
+        <f t="shared" si="0"/>
         <v>Decimal (+)</v>
       </c>
       <c r="C34" s="10" t="b">
@@ -1475,9 +1475,9 @@
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B35" s="5" t="str">
-        <f>B10</f>
+        <f t="shared" si="0"/>
         <v>Decimal (-)</v>
       </c>
       <c r="C35" s="10" t="b">
@@ -1517,9 +1517,9 @@
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B36" s="5" t="str">
-        <f>B11</f>
+        <f t="shared" si="0"/>
         <v>Text String</v>
       </c>
       <c r="C36" s="10" t="b">
@@ -1559,9 +1559,9 @@
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B37" s="5" t="str">
-        <f>B12</f>
+        <f t="shared" si="0"/>
         <v>Empty String</v>
       </c>
       <c r="C37" s="10" t="b">
@@ -1601,9 +1601,9 @@
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B38" s="5" t="b">
-        <f>B13</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C38" s="10" t="b">
@@ -1643,9 +1643,9 @@
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B39" s="5" t="b">
-        <f>B14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C39" s="10" t="b">
@@ -1685,9 +1685,9 @@
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B40" s="5" t="str">
-        <f>B15</f>
+        <f t="shared" si="0"/>
         <v>Formula (Number)</v>
       </c>
       <c r="C40" s="10" t="b">
@@ -1727,9 +1727,9 @@
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B41" s="5" t="str">
-        <f>B16</f>
+        <f t="shared" si="0"/>
         <v>Formula (Text)</v>
       </c>
       <c r="C41" s="10" t="b">
@@ -1769,9 +1769,9 @@
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B42" s="5" t="str">
-        <f>B17</f>
+        <f t="shared" si="0"/>
         <v>Formula (Logical)</v>
       </c>
       <c r="C42" s="10" t="b">
@@ -1811,9 +1811,9 @@
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B43" s="5" t="str">
-        <f>B18</f>
+        <f t="shared" si="0"/>
         <v>#N/A Error</v>
       </c>
       <c r="C43" s="10" t="b">
@@ -1853,9 +1853,9 @@
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B44" s="5" t="str">
-        <f>B19</f>
+        <f t="shared" si="0"/>
         <v>#DIV/0! Error</v>
       </c>
       <c r="C44" s="10" t="b">
@@ -1895,9 +1895,9 @@
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B45" s="5" t="str">
-        <f>B20</f>
+        <f t="shared" si="0"/>
         <v>#NUM! Error</v>
       </c>
       <c r="C45" s="10" t="b">
@@ -1937,9 +1937,9 @@
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B46" s="5" t="str">
-        <f>B21</f>
+        <f t="shared" si="0"/>
         <v>#VALUE! Error</v>
       </c>
       <c r="C46" s="10" t="b">
@@ -1979,9 +1979,9 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B47" s="5" t="str">
-        <f>B22</f>
+        <f t="shared" si="0"/>
         <v>#REF! Error</v>
       </c>
       <c r="C47" s="10" t="b">
@@ -2021,9 +2021,9 @@
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B48" s="5" t="str">
-        <f>B23</f>
+        <f t="shared" si="0"/>
         <v>Date Value</v>
       </c>
       <c r="C48" s="10" t="b">
@@ -2063,9 +2063,9 @@
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B49" s="5" t="str">
-        <f>B24</f>
+        <f t="shared" si="0"/>
         <v>Large Number</v>
       </c>
       <c r="C49" s="10" t="b">
@@ -2105,9 +2105,9 @@
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B50" s="5" t="str">
-        <f>B25</f>
+        <f t="shared" si="0"/>
         <v>Small Number</v>
       </c>
       <c r="C50" s="10" t="b">
@@ -2147,7 +2147,7 @@
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -2162,7 +2162,7 @@
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -2177,7 +2177,7 @@
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>32</v>
       </c>
@@ -2194,7 +2194,7 @@
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B54" s="9" t="s">
         <v>23</v>
       </c>
@@ -2215,9 +2215,9 @@
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B55" s="5" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B55:B75" si="1">B5</f>
         <v>Blank Cell</v>
       </c>
       <c r="C55" s="10">
@@ -2239,9 +2239,9 @@
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B56" s="5" t="str">
-        <f>B6</f>
+        <f t="shared" si="1"/>
         <v>Zero</v>
       </c>
       <c r="C56" s="10">
@@ -2263,9 +2263,9 @@
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B57" s="5" t="str">
-        <f>B7</f>
+        <f t="shared" si="1"/>
         <v>One</v>
       </c>
       <c r="C57" s="10">
@@ -2287,9 +2287,9 @@
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B58" s="5" t="str">
-        <f>B8</f>
+        <f t="shared" si="1"/>
         <v>Negative One</v>
       </c>
       <c r="C58" s="10">
@@ -2311,9 +2311,9 @@
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B59" s="5" t="str">
-        <f>B9</f>
+        <f t="shared" si="1"/>
         <v>Decimal (+)</v>
       </c>
       <c r="C59" s="10">
@@ -2335,9 +2335,9 @@
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
     </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B60" s="5" t="str">
-        <f>B10</f>
+        <f t="shared" si="1"/>
         <v>Decimal (-)</v>
       </c>
       <c r="C60" s="10">
@@ -2359,9 +2359,9 @@
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B61" s="5" t="str">
-        <f>B11</f>
+        <f t="shared" si="1"/>
         <v>Text String</v>
       </c>
       <c r="C61" s="10">
@@ -2383,9 +2383,9 @@
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B62" s="5" t="str">
-        <f>B12</f>
+        <f t="shared" si="1"/>
         <v>Empty String</v>
       </c>
       <c r="C62" s="10">
@@ -2407,9 +2407,9 @@
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B63" s="5" t="b">
-        <f>B13</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C63" s="10">
@@ -2431,9 +2431,9 @@
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
     </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B64" s="5" t="b">
-        <f>B14</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C64" s="10">
@@ -2455,9 +2455,9 @@
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
     </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B65" s="5" t="str">
-        <f>B15</f>
+        <f t="shared" si="1"/>
         <v>Formula (Number)</v>
       </c>
       <c r="C65" s="10">
@@ -2479,9 +2479,9 @@
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
     </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B66" s="5" t="str">
-        <f>B16</f>
+        <f t="shared" si="1"/>
         <v>Formula (Text)</v>
       </c>
       <c r="C66" s="10">
@@ -2503,9 +2503,9 @@
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B67" s="5" t="str">
-        <f>B17</f>
+        <f t="shared" si="1"/>
         <v>Formula (Logical)</v>
       </c>
       <c r="C67" s="10">
@@ -2527,9 +2527,9 @@
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
     </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B68" s="5" t="str">
-        <f>B18</f>
+        <f t="shared" si="1"/>
         <v>#N/A Error</v>
       </c>
       <c r="C68" s="10">
@@ -2551,9 +2551,9 @@
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
     </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B69" s="5" t="str">
-        <f>B19</f>
+        <f t="shared" si="1"/>
         <v>#DIV/0! Error</v>
       </c>
       <c r="C69" s="10">
@@ -2575,9 +2575,9 @@
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
     </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B70" s="5" t="str">
-        <f>B20</f>
+        <f t="shared" si="1"/>
         <v>#NUM! Error</v>
       </c>
       <c r="C70" s="10">
@@ -2599,9 +2599,9 @@
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B71" s="5" t="str">
-        <f>B21</f>
+        <f t="shared" si="1"/>
         <v>#VALUE! Error</v>
       </c>
       <c r="C71" s="10">
@@ -2623,9 +2623,9 @@
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
     </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B72" s="5" t="str">
-        <f>B22</f>
+        <f t="shared" si="1"/>
         <v>#REF! Error</v>
       </c>
       <c r="C72" s="10">
@@ -2647,9 +2647,9 @@
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B73" s="5" t="str">
-        <f>B23</f>
+        <f t="shared" si="1"/>
         <v>Date Value</v>
       </c>
       <c r="C73" s="10">
@@ -2671,9 +2671,9 @@
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
     </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B74" s="5" t="str">
-        <f>B24</f>
+        <f t="shared" si="1"/>
         <v>Large Number</v>
       </c>
       <c r="C74" s="10">
@@ -2695,9 +2695,9 @@
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
     </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B75" s="5" t="str">
-        <f>B25</f>
+        <f t="shared" si="1"/>
         <v>Small Number</v>
       </c>
       <c r="C75" s="10">
@@ -2719,7 +2719,7 @@
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
     </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
@@ -2734,7 +2734,7 @@
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -2749,7 +2749,7 @@
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
     </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="s">
         <v>35</v>
       </c>
@@ -2766,7 +2766,7 @@
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
     </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B79" s="9" t="s">
         <v>23</v>
       </c>
@@ -2785,9 +2785,9 @@
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B80" s="5" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B80:B100" si="2">B5</f>
         <v>Blank Cell</v>
       </c>
       <c r="C80" s="10">
@@ -2806,9 +2806,9 @@
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
     </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B81" s="5" t="str">
-        <f>B6</f>
+        <f t="shared" si="2"/>
         <v>Zero</v>
       </c>
       <c r="C81" s="10">
@@ -2827,9 +2827,9 @@
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
     </row>
-    <row r="82" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B82" s="5" t="str">
-        <f>B7</f>
+        <f t="shared" si="2"/>
         <v>One</v>
       </c>
       <c r="C82" s="10">
@@ -2848,9 +2848,9 @@
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
     </row>
-    <row r="83" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B83" s="5" t="str">
-        <f>B8</f>
+        <f t="shared" si="2"/>
         <v>Negative One</v>
       </c>
       <c r="C83" s="10">
@@ -2869,9 +2869,9 @@
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
     </row>
-    <row r="84" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B84" s="5" t="str">
-        <f>B9</f>
+        <f t="shared" si="2"/>
         <v>Decimal (+)</v>
       </c>
       <c r="C84" s="10">
@@ -2890,9 +2890,9 @@
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
     </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B85" s="5" t="str">
-        <f>B10</f>
+        <f t="shared" si="2"/>
         <v>Decimal (-)</v>
       </c>
       <c r="C85" s="10">
@@ -2911,9 +2911,9 @@
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
     </row>
-    <row r="86" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B86" s="5" t="str">
-        <f>B11</f>
+        <f t="shared" si="2"/>
         <v>Text String</v>
       </c>
       <c r="C86" s="10">
@@ -2932,9 +2932,9 @@
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
     </row>
-    <row r="87" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B87" s="5" t="str">
-        <f>B12</f>
+        <f t="shared" si="2"/>
         <v>Empty String</v>
       </c>
       <c r="C87" s="10">
@@ -2953,9 +2953,9 @@
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
     </row>
-    <row r="88" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B88" s="5" t="b">
-        <f>B13</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C88" s="10">
@@ -2974,9 +2974,9 @@
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
     </row>
-    <row r="89" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B89" s="5" t="b">
-        <f>B14</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C89" s="10">
@@ -2995,9 +2995,9 @@
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
     </row>
-    <row r="90" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B90" s="5" t="str">
-        <f>B15</f>
+        <f t="shared" si="2"/>
         <v>Formula (Number)</v>
       </c>
       <c r="C90" s="10">
@@ -3016,9 +3016,9 @@
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
     </row>
-    <row r="91" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B91" s="5" t="str">
-        <f>B16</f>
+        <f t="shared" si="2"/>
         <v>Formula (Text)</v>
       </c>
       <c r="C91" s="10">
@@ -3037,9 +3037,9 @@
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
     </row>
-    <row r="92" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B92" s="5" t="str">
-        <f>B17</f>
+        <f t="shared" si="2"/>
         <v>Formula (Logical)</v>
       </c>
       <c r="C92" s="10">
@@ -3058,9 +3058,9 @@
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
     </row>
-    <row r="93" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B93" s="5" t="str">
-        <f>B18</f>
+        <f t="shared" si="2"/>
         <v>#N/A Error</v>
       </c>
       <c r="C93" s="10" t="e">
@@ -3079,9 +3079,9 @@
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
     </row>
-    <row r="94" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B94" s="5" t="str">
-        <f>B19</f>
+        <f t="shared" si="2"/>
         <v>#DIV/0! Error</v>
       </c>
       <c r="C94" s="10" t="e">
@@ -3100,9 +3100,9 @@
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
     </row>
-    <row r="95" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B95" s="5" t="str">
-        <f>B20</f>
+        <f t="shared" si="2"/>
         <v>#NUM! Error</v>
       </c>
       <c r="C95" s="10" t="e">
@@ -3121,9 +3121,9 @@
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
     </row>
-    <row r="96" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B96" s="5" t="str">
-        <f>B21</f>
+        <f t="shared" si="2"/>
         <v>#VALUE! Error</v>
       </c>
       <c r="C96" s="10" t="e">
@@ -3142,9 +3142,9 @@
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
     </row>
-    <row r="97" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B97" s="5" t="str">
-        <f>B22</f>
+        <f t="shared" si="2"/>
         <v>#REF! Error</v>
       </c>
       <c r="C97" s="10" t="e">
@@ -3163,9 +3163,9 @@
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
     </row>
-    <row r="98" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B98" s="5" t="str">
-        <f>B23</f>
+        <f t="shared" si="2"/>
         <v>Date Value</v>
       </c>
       <c r="C98" s="10">
@@ -3184,9 +3184,9 @@
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
     </row>
-    <row r="99" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B99" s="5" t="str">
-        <f>B24</f>
+        <f t="shared" si="2"/>
         <v>Large Number</v>
       </c>
       <c r="C99" s="10">
@@ -3205,9 +3205,9 @@
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
     </row>
-    <row r="100" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B100" s="5" t="str">
-        <f>B25</f>
+        <f t="shared" si="2"/>
         <v>Small Number</v>
       </c>
       <c r="C100" s="10">
@@ -3226,7 +3226,7 @@
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
     </row>
-    <row r="101" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
@@ -3241,7 +3241,7 @@
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
     </row>
-    <row r="102" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
@@ -3256,7 +3256,7 @@
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
     </row>
-    <row r="103" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B103" s="4" t="s">
         <v>37</v>
       </c>
@@ -3273,7 +3273,7 @@
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
     </row>
-    <row r="104" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B104" s="8" t="s">
         <v>38</v>
       </c>
@@ -3292,7 +3292,7 @@
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
     </row>
-    <row r="105" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B105" s="5" t="s">
         <v>40</v>
       </c>
@@ -3312,7 +3312,7 @@
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
     </row>
-    <row r="106" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B106" s="5" t="s">
         <v>41</v>
       </c>
@@ -3332,7 +3332,7 @@
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
     </row>
-    <row r="107" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B107" s="5" t="s">
         <v>42</v>
       </c>
@@ -3352,7 +3352,7 @@
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
     </row>
-    <row r="108" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B108" s="5" t="s">
         <v>43</v>
       </c>
@@ -3372,7 +3372,7 @@
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
     </row>
-    <row r="109" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B109" s="5" t="s">
         <v>44</v>
       </c>
@@ -3392,7 +3392,7 @@
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
     </row>
-    <row r="110" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B110" s="5" t="s">
         <v>45</v>
       </c>
@@ -3412,7 +3412,7 @@
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
     </row>
-    <row r="111" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
@@ -3427,7 +3427,7 @@
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
     </row>
-    <row r="112" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
@@ -3442,7 +3442,7 @@
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
     </row>
-    <row r="113" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B113" s="4" t="s">
         <v>46</v>
       </c>
@@ -3459,7 +3459,7 @@
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
     </row>
-    <row r="114" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B114" s="9" t="s">
         <v>23</v>
       </c>
@@ -3480,9 +3480,9 @@
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
     </row>
-    <row r="115" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B115" s="5" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B115:B135" si="3">B5</f>
         <v>Blank Cell</v>
       </c>
       <c r="C115" s="10" t="str">
@@ -3504,9 +3504,9 @@
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
     </row>
-    <row r="116" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B116" s="5" t="str">
-        <f>B6</f>
+        <f t="shared" si="3"/>
         <v>Zero</v>
       </c>
       <c r="C116" s="10" t="str">
@@ -3528,9 +3528,9 @@
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
     </row>
-    <row r="117" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B117" s="5" t="str">
-        <f>B7</f>
+        <f t="shared" si="3"/>
         <v>One</v>
       </c>
       <c r="C117" s="10" t="str">
@@ -3552,9 +3552,9 @@
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
     </row>
-    <row r="118" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B118" s="5" t="str">
-        <f>B8</f>
+        <f t="shared" si="3"/>
         <v>Negative One</v>
       </c>
       <c r="C118" s="10" t="str">
@@ -3576,9 +3576,9 @@
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
     </row>
-    <row r="119" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B119" s="5" t="str">
-        <f>B9</f>
+        <f t="shared" si="3"/>
         <v>Decimal (+)</v>
       </c>
       <c r="C119" s="10" t="str">
@@ -3600,9 +3600,9 @@
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
     </row>
-    <row r="120" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B120" s="5" t="str">
-        <f>B10</f>
+        <f t="shared" si="3"/>
         <v>Decimal (-)</v>
       </c>
       <c r="C120" s="10" t="str">
@@ -3624,9 +3624,9 @@
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
     </row>
-    <row r="121" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B121" s="5" t="str">
-        <f>B11</f>
+        <f t="shared" si="3"/>
         <v>Text String</v>
       </c>
       <c r="C121" s="10" t="str">
@@ -3648,9 +3648,9 @@
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
     </row>
-    <row r="122" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B122" s="5" t="str">
-        <f>B12</f>
+        <f t="shared" si="3"/>
         <v>Empty String</v>
       </c>
       <c r="C122" s="10" t="str">
@@ -3672,9 +3672,9 @@
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
     </row>
-    <row r="123" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B123" s="5" t="b">
-        <f>B13</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="C123" s="10" t="str">
@@ -3696,9 +3696,9 @@
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
     </row>
-    <row r="124" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B124" s="5" t="b">
-        <f>B14</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="C124" s="10" t="str">
@@ -3720,9 +3720,9 @@
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
     </row>
-    <row r="125" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B125" s="5" t="str">
-        <f>B15</f>
+        <f t="shared" si="3"/>
         <v>Formula (Number)</v>
       </c>
       <c r="C125" s="10" t="str">
@@ -3744,9 +3744,9 @@
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
     </row>
-    <row r="126" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B126" s="5" t="str">
-        <f>B16</f>
+        <f t="shared" si="3"/>
         <v>Formula (Text)</v>
       </c>
       <c r="C126" s="10" t="str">
@@ -3768,9 +3768,9 @@
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
     </row>
-    <row r="127" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B127" s="5" t="str">
-        <f>B17</f>
+        <f t="shared" si="3"/>
         <v>Formula (Logical)</v>
       </c>
       <c r="C127" s="10" t="str">
@@ -3792,9 +3792,9 @@
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
     </row>
-    <row r="128" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B128" s="5" t="str">
-        <f>B18</f>
+        <f t="shared" si="3"/>
         <v>#N/A Error</v>
       </c>
       <c r="C128" s="10">
@@ -3816,9 +3816,9 @@
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
     </row>
-    <row r="129" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B129" s="5" t="str">
-        <f>B19</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0! Error</v>
       </c>
       <c r="C129" s="10">
@@ -3840,9 +3840,9 @@
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
     </row>
-    <row r="130" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B130" s="5" t="str">
-        <f>B20</f>
+        <f t="shared" si="3"/>
         <v>#NUM! Error</v>
       </c>
       <c r="C130" s="10">
@@ -3864,9 +3864,9 @@
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
     </row>
-    <row r="131" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B131" s="5" t="str">
-        <f>B21</f>
+        <f t="shared" si="3"/>
         <v>#VALUE! Error</v>
       </c>
       <c r="C131" s="10">
@@ -3888,9 +3888,9 @@
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
     </row>
-    <row r="132" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B132" s="5" t="str">
-        <f>B22</f>
+        <f t="shared" si="3"/>
         <v>#REF! Error</v>
       </c>
       <c r="C132" s="10">
@@ -3912,9 +3912,9 @@
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
     </row>
-    <row r="133" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B133" s="5" t="str">
-        <f>B23</f>
+        <f t="shared" si="3"/>
         <v>Date Value</v>
       </c>
       <c r="C133" s="10" t="str">
@@ -3936,9 +3936,9 @@
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
     </row>
-    <row r="134" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B134" s="5" t="str">
-        <f>B24</f>
+        <f t="shared" si="3"/>
         <v>Large Number</v>
       </c>
       <c r="C134" s="10" t="str">
@@ -3960,9 +3960,9 @@
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
     </row>
-    <row r="135" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B135" s="5" t="str">
-        <f>B25</f>
+        <f t="shared" si="3"/>
         <v>Small Number</v>
       </c>
       <c r="C135" s="10" t="str">
@@ -3984,7 +3984,7 @@
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
     </row>
-    <row r="136" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
@@ -3999,7 +3999,7 @@
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
     </row>
-    <row r="137" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
@@ -4014,7 +4014,7 @@
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
     </row>
-    <row r="138" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B138" s="4" t="s">
         <v>49</v>
       </c>
@@ -4031,7 +4031,7 @@
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
     </row>
-    <row r="139" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B139" s="9" t="s">
         <v>23</v>
       </c>
@@ -4072,9 +4072,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="140" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B140" s="5" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B140:B160" si="4">B5</f>
         <v>Blank Cell</v>
       </c>
       <c r="C140" s="10" t="str" cm="1">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G140" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G140" ca="1">IFERROR(CELL("filename",$C$5),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H140" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H140" ca="1">IFERROR(CELL("format",$C$5),"Error")</f>
@@ -4130,9 +4130,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B141" s="5" t="str">
-        <f>B6</f>
+        <f t="shared" si="4"/>
         <v>Zero</v>
       </c>
       <c r="C141" s="10" t="str" cm="1">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="G141" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G141" ca="1">IFERROR(CELL("filename",$C$6),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H141" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H141" ca="1">IFERROR(CELL("format",$C$6),"Error")</f>
@@ -4188,9 +4188,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B142" s="5" t="str">
-        <f>B7</f>
+        <f t="shared" si="4"/>
         <v>One</v>
       </c>
       <c r="C142" s="10" t="str" cm="1">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="G142" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G142" ca="1">IFERROR(CELL("filename",$C$7),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H142" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H142" ca="1">IFERROR(CELL("format",$C$7),"Error")</f>
@@ -4246,9 +4246,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B143" s="5" t="str">
-        <f>B8</f>
+        <f t="shared" si="4"/>
         <v>Negative One</v>
       </c>
       <c r="C143" s="10" t="str" cm="1">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="G143" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G143" ca="1">IFERROR(CELL("filename",$C$8),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H143" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H143" ca="1">IFERROR(CELL("format",$C$8),"Error")</f>
@@ -4304,9 +4304,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B144" s="5" t="str">
-        <f>B9</f>
+        <f t="shared" si="4"/>
         <v>Decimal (+)</v>
       </c>
       <c r="C144" s="10" t="str" cm="1">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="G144" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G144" ca="1">IFERROR(CELL("filename",$C$9),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H144" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H144" ca="1">IFERROR(CELL("format",$C$9),"Error")</f>
@@ -4362,9 +4362,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B145" s="5" t="str">
-        <f>B10</f>
+        <f t="shared" si="4"/>
         <v>Decimal (-)</v>
       </c>
       <c r="C145" s="10" t="str" cm="1">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="G145" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G145" ca="1">IFERROR(CELL("filename",$C$10),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H145" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H145" ca="1">IFERROR(CELL("format",$C$10),"Error")</f>
@@ -4420,9 +4420,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B146" s="5" t="str">
-        <f>B11</f>
+        <f t="shared" si="4"/>
         <v>Text String</v>
       </c>
       <c r="C146" s="10" t="str" cm="1">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="G146" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G146" ca="1">IFERROR(CELL("filename",$C$11),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H146" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H146" ca="1">IFERROR(CELL("format",$C$11),"Error")</f>
@@ -4478,9 +4478,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B147" s="5" t="str">
-        <f>B12</f>
+        <f t="shared" si="4"/>
         <v>Empty String</v>
       </c>
       <c r="C147" s="10" t="str" cm="1">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="G147" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G147" ca="1">IFERROR(CELL("filename",$C$12),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H147" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H147" ca="1">IFERROR(CELL("format",$C$12),"Error")</f>
@@ -4536,9 +4536,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B148" s="5" t="b">
-        <f>B13</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="C148" s="10" t="str" cm="1">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="G148" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G148" ca="1">IFERROR(CELL("filename",$C$13),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H148" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H148" ca="1">IFERROR(CELL("format",$C$13),"Error")</f>
@@ -4594,9 +4594,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B149" s="5" t="b">
-        <f>B14</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="C149" s="10" t="str" cm="1">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="G149" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G149" ca="1">IFERROR(CELL("filename",$C$14),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H149" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H149" ca="1">IFERROR(CELL("format",$C$14),"Error")</f>
@@ -4652,9 +4652,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B150" s="5" t="str">
-        <f>B15</f>
+        <f t="shared" si="4"/>
         <v>Formula (Number)</v>
       </c>
       <c r="C150" s="10" t="str" cm="1">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="G150" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G150" ca="1">IFERROR(CELL("filename",$C$15),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H150" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H150" ca="1">IFERROR(CELL("format",$C$15),"Error")</f>
@@ -4710,9 +4710,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B151" s="5" t="str">
-        <f>B16</f>
+        <f t="shared" si="4"/>
         <v>Formula (Text)</v>
       </c>
       <c r="C151" s="10" t="str" cm="1">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="G151" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G151" ca="1">IFERROR(CELL("filename",$C$16),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H151" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H151" ca="1">IFERROR(CELL("format",$C$16),"Error")</f>
@@ -4768,9 +4768,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B152" s="5" t="str">
-        <f>B17</f>
+        <f t="shared" si="4"/>
         <v>Formula (Logical)</v>
       </c>
       <c r="C152" s="10" t="str" cm="1">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="G152" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G152" ca="1">IFERROR(CELL("filename",$C$17),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H152" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H152" ca="1">IFERROR(CELL("format",$C$17),"Error")</f>
@@ -4826,9 +4826,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B153" s="5" t="str">
-        <f>B18</f>
+        <f t="shared" si="4"/>
         <v>#N/A Error</v>
       </c>
       <c r="C153" s="10" t="str" cm="1">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="G153" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G153" ca="1">IFERROR(CELL("filename",$C$18),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H153" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H153" ca="1">IFERROR(CELL("format",$C$18),"Error")</f>
@@ -4884,9 +4884,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B154" s="5" t="str">
-        <f>B19</f>
+        <f t="shared" si="4"/>
         <v>#DIV/0! Error</v>
       </c>
       <c r="C154" s="10" t="str" cm="1">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="G154" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G154" ca="1">IFERROR(CELL("filename",$C$19),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H154" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H154" ca="1">IFERROR(CELL("format",$C$19),"Error")</f>
@@ -4942,9 +4942,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B155" s="5" t="str">
-        <f>B20</f>
+        <f t="shared" si="4"/>
         <v>#NUM! Error</v>
       </c>
       <c r="C155" s="10" t="str" cm="1">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G155" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G155" ca="1">IFERROR(CELL("filename",$C$20),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H155" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H155" ca="1">IFERROR(CELL("format",$C$20),"Error")</f>
@@ -5000,9 +5000,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B156" s="5" t="str">
-        <f>B21</f>
+        <f t="shared" si="4"/>
         <v>#VALUE! Error</v>
       </c>
       <c r="C156" s="10" t="str" cm="1">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="G156" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G156" ca="1">IFERROR(CELL("filename",$C$21),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H156" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H156" ca="1">IFERROR(CELL("format",$C$21),"Error")</f>
@@ -5058,9 +5058,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B157" s="5" t="str">
-        <f>B22</f>
+        <f t="shared" si="4"/>
         <v>#REF! Error</v>
       </c>
       <c r="C157" s="10" t="str" cm="1">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G157" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G157" ca="1">IFERROR(CELL("filename",$C$22),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H157" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H157" ca="1">IFERROR(CELL("format",$C$22),"Error")</f>
@@ -5116,9 +5116,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B158" s="5" t="str">
-        <f>B23</f>
+        <f t="shared" si="4"/>
         <v>Date Value</v>
       </c>
       <c r="C158" s="10" t="str" cm="1">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="G158" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G158" ca="1">IFERROR(CELL("filename",$C$23),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H158" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H158" ca="1">IFERROR(CELL("format",$C$23),"Error")</f>
@@ -5174,9 +5174,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B159" s="5" t="str">
-        <f>B24</f>
+        <f t="shared" si="4"/>
         <v>Large Number</v>
       </c>
       <c r="C159" s="10" t="str" cm="1">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="G159" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G159" ca="1">IFERROR(CELL("filename",$C$24),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H159" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H159" ca="1">IFERROR(CELL("format",$C$24),"Error")</f>
@@ -5232,9 +5232,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B160" s="5" t="str">
-        <f>B25</f>
+        <f t="shared" si="4"/>
         <v>Small Number</v>
       </c>
       <c r="C160" s="10" t="str" cm="1">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="G160" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="G160" ca="1">IFERROR(CELL("filename",$C$25),"Error")</f>
-        <v>/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/information/[file.xlsx]Sheet1</v>
+        <v>C:\Users\frl\projects\calipers\verification\cases\roundtrip\formulas_information\[init.xlsx]Sheet1</v>
       </c>
       <c r="H160" s="10" t="str" cm="1">
         <f t="array" aca="1" ref="H160" ca="1">IFERROR(CELL("format",$C$25),"Error")</f>
